--- a/artfynd/A 22924-2025 artfynd.xlsx
+++ b/artfynd/A 22924-2025 artfynd.xlsx
@@ -2965,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
